--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N116_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N116_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.36696569034931</v>
+        <v>5.097131924681762</v>
       </c>
       <c r="D2" t="n">
-        <v>13.88051766175645</v>
+        <v>2.255584120035424</v>
       </c>
       <c r="E2" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F2" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.23212273911921</v>
+        <v>3.937719945106872</v>
       </c>
       <c r="D3" t="n">
-        <v>23.86624634149996</v>
+        <v>3.878265030493743</v>
       </c>
       <c r="E3" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F3" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.76262185668877</v>
+        <v>5.648926051711925</v>
       </c>
       <c r="D4" t="n">
-        <v>32.3298373162632</v>
+        <v>5.253598563892771</v>
       </c>
       <c r="E4" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F4" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.18715473562451</v>
+        <v>3.767912644538983</v>
       </c>
       <c r="D5" t="n">
-        <v>19.32062365632472</v>
+        <v>3.139601344152767</v>
       </c>
       <c r="E5" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F5" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.12035000358951</v>
+        <v>4.244556875583296</v>
       </c>
       <c r="D6" t="n">
-        <v>14.12565363598757</v>
+        <v>2.295418715847981</v>
       </c>
       <c r="E6" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F6" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.1672679147017</v>
+        <v>4.414681036139026</v>
       </c>
       <c r="D7" t="n">
-        <v>24.37275961959063</v>
+        <v>3.960573438183477</v>
       </c>
       <c r="E7" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F7" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.615773105863909</v>
+        <v>1.237563129702885</v>
       </c>
       <c r="D8" t="n">
-        <v>9.911501222974179</v>
+        <v>1.610618948733304</v>
       </c>
       <c r="E8" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F8" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.28649998930477</v>
+        <v>4.109056248262026</v>
       </c>
       <c r="D9" t="n">
-        <v>23.51502308562426</v>
+        <v>3.821191251413942</v>
       </c>
       <c r="E9" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F9" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.276536082049948</v>
+        <v>1.182437113333117</v>
       </c>
       <c r="D10" t="n">
-        <v>11.15502149542862</v>
+        <v>1.812690993007151</v>
       </c>
       <c r="E10" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F10" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.09338662244782</v>
+        <v>1.965175326147771</v>
       </c>
       <c r="D11" t="n">
-        <v>1.91803687472303</v>
+        <v>0.3116809921424923</v>
       </c>
       <c r="E11" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F11" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.10402491369992</v>
+        <v>7.329404048476237</v>
       </c>
       <c r="D12" t="n">
-        <v>36.68066694245243</v>
+        <v>5.96060837814852</v>
       </c>
       <c r="E12" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F12" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.73793114864114</v>
+        <v>1.907413811654185</v>
       </c>
       <c r="D13" t="n">
-        <v>20.65968930437715</v>
+        <v>3.357199511961286</v>
       </c>
       <c r="E13" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F13" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.27194808732907</v>
+        <v>7.194191564190975</v>
       </c>
       <c r="D14" t="n">
-        <v>34.17781497908888</v>
+        <v>5.553894934101943</v>
       </c>
       <c r="E14" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F14" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.9660457157696</v>
+        <v>3.081982428812561</v>
       </c>
       <c r="D15" t="n">
-        <v>19.59942702351962</v>
+        <v>3.184906891321939</v>
       </c>
       <c r="E15" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F15" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.94378034424403</v>
+        <v>6.165864305939656</v>
       </c>
       <c r="D16" t="n">
-        <v>36.50722490942484</v>
+        <v>5.932424047781537</v>
       </c>
       <c r="E16" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F16" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.69571225648927</v>
+        <v>4.500553241679506</v>
       </c>
       <c r="D17" t="n">
-        <v>27.96491825161158</v>
+        <v>4.544299215886882</v>
       </c>
       <c r="E17" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F17" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>47.53624832878056</v>
+        <v>7.724640353426841</v>
       </c>
       <c r="D18" t="n">
-        <v>47.90701052987608</v>
+        <v>7.784889211104864</v>
       </c>
       <c r="E18" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F18" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>27.36928319447616</v>
+        <v>4.447508519102376</v>
       </c>
       <c r="D19" t="n">
-        <v>25.843985896896</v>
+        <v>4.199647708245601</v>
       </c>
       <c r="E19" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F19" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>40.40338650924466</v>
+        <v>6.565550307752257</v>
       </c>
       <c r="D20" t="n">
-        <v>40.29044349519477</v>
+        <v>6.547197067969151</v>
       </c>
       <c r="E20" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F20" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>32.10784391162405</v>
+        <v>5.217524635638909</v>
       </c>
       <c r="D21" t="n">
-        <v>31.15741290158877</v>
+        <v>5.063079596508176</v>
       </c>
       <c r="E21" t="n">
-        <v>11.73915485849753</v>
+        <v>1.907612664505848</v>
       </c>
       <c r="F21" t="n">
-        <v>11.15741935814439</v>
+        <v>1.813080645698463</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
